--- a/HL7-AT-FHIR-Core-R5/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/HL7-AT-FHIR-Core-R5/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T14:21:13+00:00</t>
+    <t>2025-01-27T06:12:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HL7-AT-FHIR-Core-R5/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
+++ b/HL7-AT-FHIR-Core-R5/StructureDefinition-at-core-ext-address-additionalInformation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T06:12:08+00:00</t>
+    <t>2025-01-24T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
